--- a/app/src/main/assets/methodmesh/odk_templates/qrcode/example_odk_barcode_scan.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/qrcode/example_odk_barcode_scan.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R1738ea4c69274ff2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R651fe5e9794d4d90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R63ff11fe72d74ba9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R99ce503f971341d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R01cb83a4c40c4016"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rb55017c9e7e9476f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -365,309 +365,443 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="D1" t="str">
+        <x:v>hint</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
         <x:v>appearance</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="F1" t="str">
+        <x:v>required</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>relevant</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>constraint</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>constraint_message</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>calculation</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>read_only</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
         <x:v>body::intent</x:v>
-      </x:c>
-      <x:c r="F1" t="str">
-        <x:v>calculation</x:v>
-      </x:c>
-      <x:c r="G1" t="str">
-        <x:v>required</x:v>
-      </x:c>
-      <x:c r="H1" t="str">
-        <x:v>readonly</x:v>
-      </x:c>
-      <x:c r="I1" t="str">
-        <x:v>relevant</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>select_multiple barcode_format</x:v>
+        <x:v>note</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>barcode_formats_input</x:v>
+        <x:v>intro</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>Accepted code formats (optional)</x:v>
-      </x:c>
-      <x:c r="D2"/>
+        <x:v>MethodMesh Automatic code scanner — barcode.scan</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Scan a QR, Data Matrix, Aztec, PDF417 or common 1D barcode with MethodMesh. The scan is performed in the native scanner and returned only after Commit.</x:v>
+      </x:c>
       <x:c r="E2"/>
       <x:c r="F2"/>
       <x:c r="G2"/>
       <x:c r="H2"/>
       <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+      <x:c r="M2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
         <x:v>begin_group</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>code_scan</x:v>
+        <x:v>run_barcode_scan</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>Scan code</x:v>
+        <x:v>Run barcode.scan</x:v>
       </x:c>
       <x:c r="D3" t="str">
+        <x:v>One MethodMesh capability invocation. Canonical return fields are unprefixed and the shared metadata payload is captured in methodmesh_full_json.</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
         <x:v>field-list</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='barcode.scan',input_barcode_formats=${barcode_formats_input},input_payload_mode='FULL',methodmesh_return_namespace='scan',return_mode='flat')</x:v>
       </x:c>
       <x:c r="F3"/>
       <x:c r="G3"/>
       <x:c r="H3"/>
       <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+      <x:c r="M3" t="str">
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='barcode.scan',input_barcode_formats=${barcode_formats_input},input_payload_mode='FULL',return_mode='flat')</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>text</x:v>
+        <x:v>select_multiple barcode_format</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>scan_methodmesh_execution_id</x:v>
+        <x:v>barcode_formats_input</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>MethodMesh execution ID</x:v>
-      </x:c>
-      <x:c r="D4"/>
+        <x:v>Accepted code formats (optional)</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Leave blank for automatic detection of all supported formats.</x:v>
+      </x:c>
       <x:c r="E4"/>
       <x:c r="F4"/>
       <x:c r="G4"/>
-      <x:c r="H4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
+      <x:c r="H4"/>
       <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+      <x:c r="M4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>scan_methodmesh_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C5" t="str">
         <x:v>MethodMesh status</x:v>
       </x:c>
-      <x:c r="D5"/>
-      <x:c r="E5"/>
+      <x:c r="D5" t="str">
+        <x:v>Shared MethodMesh transport status.</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="F5"/>
       <x:c r="G5"/>
-      <x:c r="H5" t="str">
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="I5"/>
+      <x:c r="M5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>scan_barcode_payload</x:v>
+        <x:v>barcode_payload</x:v>
       </x:c>
       <x:c r="C6" t="str">
         <x:v>Decoded payload</x:v>
       </x:c>
-      <x:c r="D6"/>
-      <x:c r="E6"/>
+      <x:c r="D6" t="str">
+        <x:v>Primary barcode.scan result.</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="F6"/>
-      <x:c r="G6" t="str">
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="H6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="I6"/>
+      <x:c r="M6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>scan_barcode_format</x:v>
+        <x:v>barcode_format</x:v>
       </x:c>
       <x:c r="C7" t="str">
         <x:v>Detected barcode format</x:v>
       </x:c>
-      <x:c r="D7"/>
-      <x:c r="E7"/>
+      <x:c r="D7" t="str">
+        <x:v>Canonical barcode format name.</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="F7"/>
       <x:c r="G7"/>
-      <x:c r="H7" t="str">
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="I7"/>
+      <x:c r="M7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>scan_barcode_payload_kind</x:v>
+        <x:v>barcode_payload_kind</x:v>
       </x:c>
       <x:c r="C8" t="str">
         <x:v>Payload type</x:v>
       </x:c>
-      <x:c r="D8"/>
-      <x:c r="E8"/>
+      <x:c r="D8" t="str">
+        <x:v>text or url.</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="F8"/>
       <x:c r="G8"/>
-      <x:c r="H8" t="str">
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="I8"/>
+      <x:c r="M8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>scan_barcode_payload_url</x:v>
+        <x:v>barcode_payload_url</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>Payload URL</x:v>
       </x:c>
-      <x:c r="D9"/>
-      <x:c r="E9"/>
+      <x:c r="D9" t="str">
+        <x:v>Present only when the exact payload is a safe absolute HTTP/HTTPS URL.</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="F9"/>
-      <x:c r="G9"/>
-      <x:c r="H9" t="str">
+      <x:c r="G9" t="str">
+        <x:v>${barcode_payload_kind} = 'url'</x:v>
+      </x:c>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="I9" t="str">
-        <x:v>${scan_barcode_payload_kind} = 'url'</x:v>
-      </x:c>
+      <x:c r="M9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>text</x:v>
+        <x:v>hidden</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>scan_barcode_scan_time_iso</x:v>
+        <x:v>barcode_payload_sha256</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>Scan time</x:v>
-      </x:c>
-      <x:c r="D10"/>
+        <x:v>Barcode payload SHA-256</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>SHA-256 of the exact decoded payload.</x:v>
+      </x:c>
       <x:c r="E10"/>
       <x:c r="F10"/>
       <x:c r="G10"/>
-      <x:c r="H10" t="str">
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="I10"/>
+      <x:c r="M10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>text</x:v>
+        <x:v>hidden</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>scan_barcode_source</x:v>
+        <x:v>verification_evidence_format</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>Capture source</x:v>
-      </x:c>
-      <x:c r="D11"/>
+        <x:v>Verification evidence format</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Evidence recipe identifier.</x:v>
+      </x:c>
       <x:c r="E11"/>
       <x:c r="F11"/>
       <x:c r="G11"/>
-      <x:c r="H11" t="str">
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="I11"/>
+      <x:c r="M11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
         <x:v>hidden</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>scan_barcode_payload_sha256</x:v>
-      </x:c>
-      <x:c r="C12"/>
-      <x:c r="D12"/>
+        <x:v>verification_evidence_hash</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Verification evidence hash</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Evidence hash for this payload.</x:v>
+      </x:c>
       <x:c r="E12"/>
       <x:c r="F12"/>
       <x:c r="G12"/>
       <x:c r="H12"/>
       <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>hidden</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>scan_verification_evidence_format</x:v>
-      </x:c>
-      <x:c r="C13"/>
-      <x:c r="D13"/>
-      <x:c r="E13"/>
+        <x:v>barcode_scan_time_iso</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Scan time</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>ISO-8601 capture time.</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="F13"/>
       <x:c r="G13"/>
       <x:c r="H13"/>
       <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>hidden</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>scan_verification_evidence_hash</x:v>
-      </x:c>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
+        <x:v>barcode_source</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Capture source</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Scanner/source identifier.</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="F14"/>
       <x:c r="G14"/>
       <x:c r="H14"/>
       <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>hidden</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>scan_methodmesh_full_json</x:v>
-      </x:c>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
+        <x:v>methodmesh_full_json</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>MethodMesh full JSON</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Complete MethodMesh execution/audit payload returned for the handled roundtrip.</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="F15"/>
       <x:c r="G15"/>
       <x:c r="H15"/>
       <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>note</x:v>
-      </x:c>
-      <x:c r="B16" t="str">
-        <x:v>barcode_summary</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>Scanned: ${scan_barcode_payload}</x:v>
-      </x:c>
+        <x:v>end_group</x:v>
+      </x:c>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
       <x:c r="D16"/>
       <x:c r="E16"/>
       <x:c r="F16"/>
       <x:c r="G16"/>
       <x:c r="H16"/>
-      <x:c r="I16" t="str">
-        <x:v>${scan_barcode_payload} != ''</x:v>
-      </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+      <x:c r="M16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>end_group</x:v>
-      </x:c>
-      <x:c r="B17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+        <x:v>note</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>return_summary</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>MethodMesh return captured. Status: ${methodmesh_status}</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Decoded payload: ${barcode_payload}</x:v>
+      </x:c>
       <x:c r="E17"/>
       <x:c r="F17"/>
-      <x:c r="G17"/>
+      <x:c r="G17" t="str">
+        <x:v>${barcode_payload} != ''</x:v>
+      </x:c>
       <x:c r="H17"/>
       <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
+      <x:c r="M17"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -887,6 +1021,8 @@
       <x:c r="D1" s="3" t="str">
         <x:v>instance_name</x:v>
       </x:c>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -896,11 +1032,13 @@
         <x:v>barcode_scan</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>2026090703</x:v>
+        <x:v>2026091201</x:v>
       </x:c>
       <x:c r="D2" t="str">
-        <x:v>${scan_barcode_payload}</x:v>
-      </x:c>
+        <x:v>${barcode_payload}</x:v>
+      </x:c>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
